--- a/XBRL-template-MPERS/Company/01-SOFP-CuNonCu.xlsx
+++ b/XBRL-template-MPERS/Company/01-SOFP-CuNonCu.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -447,506 +447,639 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on statement of financial position [abstract]</t>
+          <t>Disclosure on statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement of financial position [abstract]</t>
+          <t>Statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of financial position [table]</t>
+          <t>Assets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Non-current assets</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
-        </is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>'SOFP-Sub-CuNonCu'!B26</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>'SOFP-Sub-CuNonCu'!C26</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
-        </is>
+          <t>Investment properties</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>'SOFP-Sub-CuNonCu'!B33</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>'SOFP-Sub-CuNonCu'!C33</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement of financial position [line items]</t>
+          <t>Biological assets</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Assets [abstract]</t>
-        </is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>'SOFP-Sub-CuNonCu'!B40</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>'SOFP-Sub-CuNonCu'!C40</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Non-current assets [abstract]</t>
-        </is>
+          <t>Investments in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>'SOFP-Sub-CuNonCu'!B46</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>'SOFP-Sub-CuNonCu'!C46</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
-        </is>
+          <t>Investments in associates</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>'SOFP-Sub-CuNonCu'!B53</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>'SOFP-Sub-CuNonCu'!C53</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Investment properties</t>
-        </is>
+          <t>Investments in joint ventures</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>'SOFP-Sub-CuNonCu'!B60</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>'SOFP-Sub-CuNonCu'!C60</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Biological assets</t>
+          <t>Other investments</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
-        </is>
+          <t>Trade and other non-current receivables</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>'SOFP-Sub-CuNonCu'!B84</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>'SOFP-Sub-CuNonCu'!C84</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Investments in subsidiaries</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Investments in associates</t>
+          <t>Other non-current assets</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Investments in joint ventures</t>
-        </is>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current assets</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other investments</t>
+          <t>Current assets</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Trade and other non-current receivables</t>
-        </is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>'SOFP-Sub-CuNonCu'!B91</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>'SOFP-Sub-CuNonCu'!C91</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>Biological assets</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Other non-current assets</t>
+          <t>Other investments</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current assets</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Trade and other current receivables</t>
         </is>
       </c>
       <c r="B23">
-        <f>1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22</f>
+        <f>'SOFP-Sub-CuNonCu'!B122</f>
         <v/>
       </c>
       <c r="C23">
-        <f>1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22</f>
+        <f>'SOFP-Sub-CuNonCu'!C122</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Current assets [abstract]</t>
+          <t>Current tax assets</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>Derivative financial assets</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biological assets</t>
-        </is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>'SOFP-Sub-CuNonCu'!B138</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>'SOFP-Sub-CuNonCu'!C138</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Other investments</t>
+          <t>Other current assets</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Trade and other current receivables</t>
-        </is>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>*Total current assets</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>1*B20+1*B21+1*B22+1*B23+1*B24+1*B25+1*B26+1*B27</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>1*C20+1*C21+1*C22+1*C23+1*C24+1*C25+1*C26+1*C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Current tax assets</t>
-        </is>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>*Total assets</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>1*B7+1*B8+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B20+1*B22+1*B23+1*B24+1*B25+1*B26+1*B27+1*B10+1*B9+1*B21</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>1*C7+1*C8+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C20+1*C22+1*C23+1*C24+1*C25+1*C26+1*C27+1*C10+1*C9+1*C21</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Derivative financial assets</t>
+          <t>Equity and liabilities</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Equity</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Other current assets</t>
-        </is>
+          <t>Issued capital</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>'SOFP-Sub-CuNonCu'!B143</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>'SOFP-Sub-CuNonCu'!C143</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>*Total current assets</t>
-        </is>
-      </c>
-      <c r="B33">
-        <f>1*B25+1*B26+1*B27+1*B28+1*B29+1*B30+1*B31+1*B32</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>1*C25+1*C26+1*C27+1*C28+1*C29+1*C30+1*C31+1*C32</f>
-        <v/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>*Total assets</t>
-        </is>
-      </c>
-      <c r="B34">
-        <f>1*B12+1*B13+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B25+1*B27+1*B28+1*B29+1*B30+1*B31+1*B32+1*B15+1*B14+1*B26</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>1*C12+1*C13+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C25+1*C27+1*C28+1*C29+1*C30+1*C31+1*C32+1*C15+1*C14+1*C26</f>
-        <v/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Treasury shares</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Equity and liabilities [abstract]</t>
-        </is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>'SOFP-Sub-CuNonCu'!B154</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>'SOFP-Sub-CuNonCu'!C154</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Equity [abstract]</t>
-        </is>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>*Total equity attributable to owners</t>
+        </is>
+      </c>
+      <c r="B36">
+        <f>1*B32+1*B33+-1*B34+1*B35</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>1*C32+1*C33+-1*C34+1*C35</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Issued capital</t>
-        </is>
+          <t>Equity - other components</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>'SOFP-Sub-CuNonCu'!B160</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>'SOFP-Sub-CuNonCu'!C160</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Retained earnings</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Treasury shares</t>
-        </is>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>*Total equity</t>
+        </is>
+      </c>
+      <c r="B39">
+        <f>1*B32+1*B33+-1*B34+1*B35+1*B37+1*B38</f>
+        <v/>
+      </c>
+      <c r="C39">
+        <f>1*C32+1*C33+-1*C34+1*C35+1*C37+1*C38</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Reserves</t>
+          <t>Liabilities</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>*Total equity attributable to owners</t>
-        </is>
-      </c>
-      <c r="B41">
-        <f>1*B37+1*B38+-1*B39+1*B40</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>1*C37+1*C38+-1*C39+1*C40</f>
-        <v/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Non-current liabilities</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equity - other components</t>
-        </is>
+          <t>Loans and borrowings</t>
+        </is>
+      </c>
+      <c r="B42">
+        <f>'SOFP-Sub-CuNonCu'!B176</f>
+        <v/>
+      </c>
+      <c r="C42">
+        <f>'SOFP-Sub-CuNonCu'!C176</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
+          <t>Employee benefits</t>
+        </is>
+      </c>
+      <c r="B43">
+        <f>'SOFP-Sub-CuNonCu'!B184</f>
+        <v/>
+      </c>
+      <c r="C43">
+        <f>'SOFP-Sub-CuNonCu'!C184</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>*Total equity</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Provisions</t>
         </is>
       </c>
       <c r="B44">
-        <f>1*B37+1*B38+-1*B39+1*B40+1*B42+1*B43</f>
+        <f>'SOFP-Sub-CuNonCu'!B192</f>
         <v/>
       </c>
       <c r="C44">
-        <f>1*C37+1*C38+-1*C39+1*C40+1*C42+1*C43</f>
+        <f>'SOFP-Sub-CuNonCu'!C192</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Liabilities [abstract]</t>
+          <t>Deferred tax liabilities</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Non-current liabilities [abstract]</t>
-        </is>
+          <t>Trade and other non-current payables</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>'SOFP-Sub-CuNonCu'!B217</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>'SOFP-Sub-CuNonCu'!C217</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Loans and borrowings</t>
+          <t>Other non-current liabilities</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Employee benefits</t>
-        </is>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current liabilities</t>
+        </is>
+      </c>
+      <c r="B48">
+        <f>1*B42+1*B43+1*B44+1*B45+1*B46+1*B47</f>
+        <v/>
+      </c>
+      <c r="C48">
+        <f>1*C42+1*C43+1*C44+1*C45+1*C46+1*C47</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Current liabilities</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deferred tax liabilities</t>
-        </is>
+          <t>Loans and borrowings</t>
+        </is>
+      </c>
+      <c r="B50">
+        <f>'SOFP-Sub-CuNonCu'!B235</f>
+        <v/>
+      </c>
+      <c r="C50">
+        <f>'SOFP-Sub-CuNonCu'!C235</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Trade and other non-current payables</t>
-        </is>
+          <t>Employee benefits</t>
+        </is>
+      </c>
+      <c r="B51">
+        <f>'SOFP-Sub-CuNonCu'!B243</f>
+        <v/>
+      </c>
+      <c r="C51">
+        <f>'SOFP-Sub-CuNonCu'!C243</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Other non-current liabilities</t>
-        </is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B52">
+        <f>'SOFP-Sub-CuNonCu'!B251</f>
+        <v/>
+      </c>
+      <c r="C52">
+        <f>'SOFP-Sub-CuNonCu'!C251</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current liabilities</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Trade and other current payables</t>
         </is>
       </c>
       <c r="B53">
-        <f>1*B47+1*B48+1*B49+1*B50+1*B51+1*B52</f>
+        <f>'SOFP-Sub-CuNonCu'!B277</f>
         <v/>
       </c>
       <c r="C53">
-        <f>1*C47+1*C48+1*C49+1*C50+1*C51+1*C52</f>
+        <f>'SOFP-Sub-CuNonCu'!C277</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Current liabilities [abstract]</t>
+          <t>Current tax liabilities</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Loans and borrowings</t>
+          <t>Derivative financial liabilities</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Provisions</t>
-        </is>
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>*Total current liabilities</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>1*B50+1*B51+1*B52+1*B53+1*B54+1*B55+1*B56</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>1*C50+1*C51+1*C52+1*C53+1*C54+1*C55+1*C56</f>
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Trade and other current payables</t>
-        </is>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>*Total liabilities</t>
+        </is>
+      </c>
+      <c r="B58">
+        <f>1*B50+1*B51+1*B52+1*B53+1*B54+1*B55+1*B56+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>1*C50+1*C51+1*C52+1*C53+1*C54+1*C55+1*C56+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47</f>
+        <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Current tax liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Derivative financial liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Other current liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>*Total current liabilities</t>
-        </is>
-      </c>
-      <c r="B62">
-        <f>1*B55+1*B56+1*B57+1*B58+1*B59+1*B60+1*B61</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>1*C55+1*C56+1*C57+1*C58+1*C59+1*C60+1*C61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>*Total liabilities</t>
-        </is>
-      </c>
-      <c r="B63">
-        <f>1*B55+1*B56+1*B57+1*B58+1*B59+1*B60+1*B61+1*B47+1*B48+1*B49+1*B50+1*B51+1*B52</f>
-        <v/>
-      </c>
-      <c r="C63">
-        <f>1*C55+1*C56+1*C57+1*C58+1*C59+1*C60+1*C61+1*C47+1*C48+1*C49+1*C50+1*C51+1*C52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>*Total equity and liabilities</t>
         </is>
       </c>
-      <c r="B64">
-        <f>1*B44+1*B63</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>1*C44+1*C63</f>
+      <c r="B59">
+        <f>1*B39+1*B58</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>1*C39+1*C58</f>
         <v/>
       </c>
     </row>
@@ -961,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D282"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -990,2328 +1123,2293 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on sub-classification of assets, liabilities and equity [abstract]</t>
+          <t>Disclosure on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement on sub-classification of assets, liabilities and equity [abstract]</t>
+          <t>Statement on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement on sub-classification of assets, liabilities and equity [table]</t>
+          <t>Sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Land and buildings</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Land</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement on sub-classification of assets, liabilities and equity [line items]</t>
+          <t>Freehold land</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sub-classification of assets, liabilities and equity [abstract]</t>
+          <t>Long term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Property, plant and equipment [abstract]</t>
+          <t>Short term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Land and buildings [abstract]</t>
-        </is>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>*Total land</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>1*B9+1*B10+1*B11</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>1*C9+1*C10+1*C11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Land [abstract]</t>
+          <t>Buildings</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Freehold land</t>
+          <t>Building on freehold land</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Long term leasehold land</t>
+          <t>Building on long term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Short term leasehold land</t>
+          <t>Building on short term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>*Total land</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>1*B14+1*B15+1*B16</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>1*C14+1*C15+1*C16</f>
-        <v/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Leased properties</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Buildings [abstract]</t>
-        </is>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>*Total buildings</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>1*B14+1*B15+1*B16+1*B17</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>1*C14+1*C15+1*C16+1*C17</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Building on freehold land</t>
-        </is>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>*Total land and buildings</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>1*B12+1*B18</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>1*C12+1*C18</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Building on long term leasehold land</t>
+          <t>Machinery</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Building on short term leasehold land</t>
+          <t>Vehicles</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Leased properties</t>
+          <t>Office equipment, fixture and fittings</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>*Total buildings</t>
-        </is>
-      </c>
-      <c r="B23">
-        <f>1*B19+1*B20+1*B21+1*B22</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>1*C19+1*C20+1*C21+1*C22</f>
-        <v/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Plant and equipment</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>*Total land and buildings</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>1*B17+1*B23</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>1*C17+1*C23</f>
-        <v/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Construction in progress/Asset work-in progress</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Other property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Vehicles</t>
-        </is>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>*Total property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>1*B19+1*B20+1*B21+1*B22+1*B23+1*B24+1*B25</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>1*C19+1*C20+1*C21+1*C22+1*C23+1*C24+1*C25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Office equipment, fixture and fittings</t>
+          <t>Investment properties</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plant and equipment</t>
+          <t>Freehold land</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Construction in progress/Asset work-in progress</t>
+          <t>Long term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other property, plant and equipment</t>
+          <t>Short term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>*Total property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B31">
-        <f>1*B24+1*B25+1*B26+1*B27+1*B28+1*B29+1*B30</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>1*C24+1*C25+1*C26+1*C27+1*C28+1*C29+1*C30</f>
-        <v/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Investment properties [abstract]</t>
+          <t>Other investment property</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Freehold land</t>
-        </is>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>*Total investment properties</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>1*B28+1*B29+1*B30+1*B31+1*B32</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>1*C28+1*C29+1*C30+1*C31+1*C32</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Long term leasehold land</t>
+          <t>Intangible assets and goodwill</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Short term leasehold land</t>
+          <t>Intangible assets other than goodwill</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Copyrights, patents and other industrial property rights, service and operating rights</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Other investment property</t>
+          <t>Other intangible assets</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>*Total investment properties</t>
+          <t>*Total intangible assets other than goodwill</t>
         </is>
       </c>
       <c r="B38">
-        <f>1*B33+1*B34+1*B35+1*B36+1*B37</f>
+        <f>1*B36+1*B37</f>
         <v/>
       </c>
       <c r="C38">
-        <f>1*C33+1*C34+1*C35+1*C36+1*C37</f>
+        <f>1*C36+1*C37</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intangible assets and goodwill [abstract]</t>
+          <t>Goodwill</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Intangible assets other than goodwill [abstract]</t>
-        </is>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>*Total intangible assets and goodwill</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>1*B39+1*B38</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>1*C39+1*C38</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Copyrights, patents and other industrial property rights, service and operating rights</t>
+          <t>Investments in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Other intangible assets</t>
+          <t>Unquoted shares, net of impairment losses</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>*Total intangible assets other than goodwill</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>1*B41+1*B42</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>1*C41+1*C42</f>
-        <v/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Quoted shares in Malaysia</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Quoted shares outside Malaysia</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>*Total intangible assets and goodwill</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f>1*B44+1*B43</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>1*C44+1*C43</f>
-        <v/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other investments in subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Investments in subsidiaries [abstract]</t>
-        </is>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>*Total investments in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>1*B42+1*B43+1*B44+1*B45</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>1*C42+1*C43+1*C44+1*C45</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unquoted shares, net of impairment losses</t>
+          <t>Investments in associates</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quoted shares in Malaysia</t>
+          <t>Unquoted shares, net of impairment losses</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quoted shares outside Malaysia</t>
+          <t>Quoted shares in Malaysia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Other investments in subsidiaries</t>
+          <t>Quoted shares outside Malaysia</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>*Total investments in subsidiaries</t>
-        </is>
-      </c>
-      <c r="B51">
-        <f>1*B47+1*B48+1*B49+1*B50</f>
-        <v/>
-      </c>
-      <c r="C51">
-        <f>1*C47+1*C48+1*C49+1*C50</f>
-        <v/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of post-acquisition profits and reserves</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Investments in associates [abstract]</t>
+          <t>Other investments in associates</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Unquoted shares, net of impairment losses</t>
-        </is>
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>*Total investments in associates</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>1*B48+1*B49+1*B50+1*B51+1*B52</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>1*C48+1*C49+1*C50+1*C51+1*C52</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quoted shares in Malaysia</t>
+          <t>Investments in joint ventures</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quoted shares outside Malaysia</t>
+          <t>Unquoted shares, net of impairment losses</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Share of post-acquisition profits and reserves</t>
+          <t>Quoted shares in Malaysia</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Other investments in associates</t>
+          <t>Quoted shares outside Malaysia</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>*Total investments in associates</t>
-        </is>
-      </c>
-      <c r="B58">
-        <f>1*B53+1*B54+1*B55+1*B56+1*B57</f>
-        <v/>
-      </c>
-      <c r="C58">
-        <f>1*C53+1*C54+1*C55+1*C56+1*C57</f>
-        <v/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of post-acquisition profits and reserves</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Investments in joint ventures [abstract]</t>
+          <t>Other investments in joint ventures</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unquoted shares, net of impairment losses</t>
-        </is>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>*Total of investments in joint ventures</t>
+        </is>
+      </c>
+      <c r="B60">
+        <f>1*B55+1*B56+1*B57+1*B58+1*B59</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>1*C55+1*C56+1*C57+1*C58+1*C59</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Quoted shares in Malaysia</t>
+          <t>Trade and other non-current receivables</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Quoted shares outside Malaysia</t>
+          <t>Non-current trade receivables</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Share of post-acquisition profits and reserves</t>
+          <t>Trade receivables due from holding company</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Other investments in joint ventures</t>
+          <t>Trade receivables due from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>*Total of investments in joint ventures</t>
-        </is>
-      </c>
-      <c r="B65">
-        <f>1*B60+1*B61+1*B62+1*B63+1*B64</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>1*C60+1*C61+1*C62+1*C63+1*C64</f>
-        <v/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Trade receivables from associates</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Trade and other non-current receivables [abstract]</t>
+          <t>Trade receivables due from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Non-current trade receivables [abstract]</t>
+          <t>Trade receivables due from other related parties</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Trade receivables due from holding company</t>
+          <t>Other non-current trade receivables</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Trade receivables due from subsidiaries</t>
-        </is>
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current trade receivables</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>1*B63+1*B64+1*B65+1*B66+1*B67+1*B68</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>1*C63+1*C64+1*C65+1*C66+1*C67+1*C68</f>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Trade receivables from associates</t>
+          <t>Other non-current receivables</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Trade receivables due from joint ventures</t>
+          <t>Other non-current receivables due from related parties</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Trade receivables due from other related parties</t>
+          <t>Other receivables due from holding company</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Other non-current trade receivables</t>
+          <t>Other receivables due from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current trade receivables</t>
-        </is>
-      </c>
-      <c r="B74">
-        <f>1*B68+1*B69+1*B70+1*B71+1*B72+1*B73</f>
-        <v/>
-      </c>
-      <c r="C74">
-        <f>1*C68+1*C69+1*C70+1*C71+1*C72+1*C73</f>
-        <v/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Other receivables due from associates</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Other non-current receivables [abstract]</t>
+          <t>Other receivables due from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Other non-current receivables due from related parties [abstract]</t>
+          <t>Other receivables due from other related parties</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Other receivables due from holding company</t>
-        </is>
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>*Total other non-current receivables due from related parties</t>
+        </is>
+      </c>
+      <c r="B77">
+        <f>1*B72+1*B73+1*B74+1*B75+1*B76</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>1*C72+1*C73+1*C74+1*C75+1*C76</f>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Other receivables due from subsidiaries</t>
+          <t>Non-current non-trade receivables</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Other receivables due from associates</t>
+          <t>Accrued income</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Other receivables due from joint ventures</t>
+          <t>Lease and hire purchase receivables</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Other receivables due from other related parties</t>
+          <t>Other non-current non-trade receivables</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>*Total other non-current receivables due from related parties</t>
+          <t>*Total other non-current non-trade receivables</t>
         </is>
       </c>
       <c r="B82">
-        <f>1*B77+1*B78+1*B79+1*B80+1*B81</f>
+        <f>1*B79+1*B80+1*B81</f>
         <v/>
       </c>
       <c r="C82">
-        <f>1*C77+1*C78+1*C79+1*C80+1*C81</f>
+        <f>1*C79+1*C80+1*C81</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Non-current non-trade receivables [abstract]</t>
-        </is>
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>*Total other non-current receivables</t>
+        </is>
+      </c>
+      <c r="B83">
+        <f>1*B82</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>1*C82</f>
+        <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Accrued income</t>
-        </is>
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>*Total trade and other non-current receivables</t>
+        </is>
+      </c>
+      <c r="B84">
+        <f>1*B69+1*B83+1*B77</f>
+        <v/>
+      </c>
+      <c r="C84">
+        <f>1*C69+1*C83+1*C77</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lease and hire purchase receivables</t>
+          <t>Inventories</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Other non-current non-trade receivables</t>
+          <t>Raw materials</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
-        <is>
-          <t>*Total other non-current non-trade receivables</t>
-        </is>
-      </c>
-      <c r="B87">
-        <f>1*B84+1*B85+1*B86</f>
-        <v/>
-      </c>
-      <c r="C87">
-        <f>1*C84+1*C85+1*C86</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Work in progress</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>*Total other non-current receivables</t>
-        </is>
-      </c>
-      <c r="B88">
-        <f>1*B87</f>
-        <v/>
-      </c>
-      <c r="C88">
-        <f>1*C87</f>
-        <v/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Finished goods</t>
+        </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>*Total trade and other non-current receivables</t>
-        </is>
-      </c>
-      <c r="B89">
-        <f>1*B74+1*B88+1*B82</f>
-        <v/>
-      </c>
-      <c r="C89">
-        <f>1*C74+1*C88+1*C82</f>
-        <v/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Spare parts</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Inventories [abstract]</t>
+          <t>Other inventories</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Raw materials</t>
-        </is>
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>*Total inventories</t>
+        </is>
+      </c>
+      <c r="B91">
+        <f>1*B86+1*B87+1*B88+1*B89+1*B90</f>
+        <v/>
+      </c>
+      <c r="C91">
+        <f>1*C86+1*C87+1*C88+1*C89+1*C90</f>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Work in progress</t>
+          <t>Trade and other current receivables</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Finished goods</t>
+          <t>Current trade receivables</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Spare parts</t>
+          <t>Trade receivables due from contract customers</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Other inventories</t>
+          <t>Trade receivables due from holding company</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>*Total inventories</t>
-        </is>
-      </c>
-      <c r="B96">
-        <f>1*B91+1*B92+1*B93+1*B94+1*B95</f>
-        <v/>
-      </c>
-      <c r="C96">
-        <f>1*C91+1*C92+1*C93+1*C94+1*C95</f>
-        <v/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Trade receivables due from subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Trade and other current receivables [abstract]</t>
+          <t>Trade receivables due from associates</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Current trade receivables [abstract]</t>
+          <t>Trade receivables due from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Trade receivables due from contract customers</t>
+          <t>Trade receivables due from other related parties</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Trade receivables due from holding company</t>
+          <t>Other current trade receivables</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Trade receivables due from subsidiaries</t>
-        </is>
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>*Total current trade receivables</t>
+        </is>
+      </c>
+      <c r="B101">
+        <f>1*B94+1*B95+1*B96+1*B97+1*B98+1*B99+1*B100</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>1*C94+1*C95+1*C96+1*C97+1*C98+1*C99+1*C100</f>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Trade receivables due from associates</t>
+          <t>Other current receivables</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Trade receivables due from joint ventures</t>
+          <t>Current other receivables due from related parties</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Trade receivables due from other related parties</t>
+          <t>Other receivables due from holding company</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Other current trade receivables</t>
+          <t>Other receivables due from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr">
-        <is>
-          <t>*Total current trade receivables</t>
-        </is>
-      </c>
-      <c r="B106">
-        <f>1*B99+1*B100+1*B101+1*B102+1*B103+1*B104+1*B105</f>
-        <v/>
-      </c>
-      <c r="C106">
-        <f>1*C99+1*C100+1*C101+1*C102+1*C103+1*C104+1*C105</f>
-        <v/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Other receivables due from associates</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Other current receivables [abstract]</t>
+          <t>Other receivables due from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Current other receivables due from related parties [abstract]</t>
+          <t>Other receivables due from other related parties</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Other receivables due from holding company</t>
-        </is>
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>*Total current other receivables due from related parties</t>
+        </is>
+      </c>
+      <c r="B109">
+        <f>1*B104+1*B105+1*B106+1*B107+1*B108</f>
+        <v/>
+      </c>
+      <c r="C109">
+        <f>1*C104+1*C105+1*C106+1*C107+1*C108</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Other receivables due from subsidiaries</t>
+          <t>Current prepayments and current accrued income</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Other receivables due from associates</t>
+          <t>Prepayments</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Other receivables due from joint ventures</t>
+          <t>Accrued income</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Other receivables due from other related parties</t>
-        </is>
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>*Total current prepayments and current accrued income</t>
+        </is>
+      </c>
+      <c r="B113">
+        <f>1*B111+1*B112</f>
+        <v/>
+      </c>
+      <c r="C113">
+        <f>1*C111+1*C112</f>
+        <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="inlineStr">
-        <is>
-          <t>*Total current other receivables due from related parties</t>
-        </is>
-      </c>
-      <c r="B114">
-        <f>1*B109+1*B110+1*B111+1*B112+1*B113</f>
-        <v/>
-      </c>
-      <c r="C114">
-        <f>1*C109+1*C110+1*C111+1*C112+1*C113</f>
-        <v/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Current non-trade receivables</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Current prepayments and current accrued income [abstract]</t>
+          <t>Interest receivables</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Prepayments</t>
+          <t>Deposits</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Accrued income</t>
+          <t>Dividend receivables</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t>*Total current prepayments and current accrued income</t>
-        </is>
-      </c>
-      <c r="B118">
-        <f>1*B116+1*B117</f>
-        <v/>
-      </c>
-      <c r="C118">
-        <f>1*C116+1*C117</f>
-        <v/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Lease and hire purchase receivables</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Current non-trade receivables [abstract]</t>
+          <t>Other current non-trade receivables</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Interest receivables</t>
-        </is>
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>*Total non trade receivables</t>
+        </is>
+      </c>
+      <c r="B120">
+        <f>1*B115+1*B116+1*B117+1*B118+1*B119</f>
+        <v/>
+      </c>
+      <c r="C120">
+        <f>1*C115+1*C116+1*C117+1*C118+1*C119</f>
+        <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Deposits</t>
-        </is>
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>*Total other current receivables</t>
+        </is>
+      </c>
+      <c r="B121">
+        <f>1*B109+1*B113+1*B120</f>
+        <v/>
+      </c>
+      <c r="C121">
+        <f>1*C109+1*C113+1*C120</f>
+        <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Dividend receivables</t>
-        </is>
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>*Total trade and other current receivables</t>
+        </is>
+      </c>
+      <c r="B122">
+        <f>1*B101+1*B121</f>
+        <v/>
+      </c>
+      <c r="C122">
+        <f>1*C101+1*C121</f>
+        <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lease and hire purchase receivables</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Other current non-trade receivables</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>*Total non trade receivables</t>
-        </is>
-      </c>
-      <c r="B125">
-        <f>1*B120+1*B121+1*B122+1*B123+1*B124</f>
-        <v/>
-      </c>
-      <c r="C125">
-        <f>1*C120+1*C121+1*C122+1*C123+1*C124</f>
-        <v/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Cash in hand</t>
+        </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
-        <is>
-          <t>*Total other current receivables</t>
-        </is>
-      </c>
-      <c r="B126">
-        <f>1*B114+1*B118+1*B125</f>
-        <v/>
-      </c>
-      <c r="C126">
-        <f>1*C114+1*C118+1*C125</f>
-        <v/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Balances with banks</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>*Total trade and other current receivables</t>
+          <t>*Total cash</t>
         </is>
       </c>
       <c r="B127">
-        <f>1*B106+1*B126</f>
+        <f>1*B125+1*B126</f>
         <v/>
       </c>
       <c r="C127">
-        <f>1*C106+1*C126</f>
+        <f>1*C125+1*C126</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents [abstract]</t>
+          <t>Cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cash [abstract]</t>
+          <t>Deposits placed with licensed banks</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cash in hand</t>
+          <t>Deposit placed with other corporations</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Balances with banks</t>
+          <t>Fixed deposits with financial institutions</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>*Total cash</t>
-        </is>
-      </c>
-      <c r="B132">
-        <f>1*B130+1*B131</f>
-        <v/>
-      </c>
-      <c r="C132">
-        <f>1*C130+1*C131</f>
-        <v/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Cash equivalents with other financial institutions</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cash equivalents [abstract]</t>
+          <t>Short-term deposits</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Deposits placed with licensed banks</t>
+          <t>Short-term investments</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Deposit placed with other corporations</t>
+          <t>Other banking arrangements</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Fixed deposits with financial institutions</t>
-        </is>
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>*Total cash equivalents</t>
+        </is>
+      </c>
+      <c r="B136">
+        <f>1*B129+1*B130+1*B131+1*B132+1*B133+1*B134+1*B135</f>
+        <v/>
+      </c>
+      <c r="C136">
+        <f>1*C129+1*C130+1*C131+1*C132+1*C133+1*C134+1*C135</f>
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cash equivalents with other financial institutions</t>
+          <t>Other cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Short-term deposits</t>
-        </is>
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>*Total cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B138">
+        <f>1*B127+1*B136+1*B137</f>
+        <v/>
+      </c>
+      <c r="C138">
+        <f>1*C127+1*C136+1*C137</f>
+        <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Short-term investments</t>
+          <t>Issued capital</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Other banking arrangements</t>
+          <t>Capital from ordinary shares</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>*Total cash equivalents</t>
-        </is>
-      </c>
-      <c r="B141">
-        <f>1*B134+1*B135+1*B136+1*B137+1*B138+1*B139+1*B140</f>
-        <v/>
-      </c>
-      <c r="C141">
-        <f>1*C134+1*C135+1*C136+1*C137+1*C138+1*C139+1*C140</f>
-        <v/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Capital from redeemable preference shares</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Other cash and cash equivalents</t>
+          <t>Capital from non-redeemable preference shares</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>*Total cash and cash equivalents</t>
+          <t>*Total issued capital</t>
         </is>
       </c>
       <c r="B143">
-        <f>1*B132+1*B141+1*B142</f>
+        <f>1*B140+1*B141+1*B142</f>
         <v/>
       </c>
       <c r="C143">
-        <f>1*C132+1*C141+1*C142</f>
+        <f>1*C140+1*C141+1*C142</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Issued capital [abstract]</t>
+          <t>Reserves</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Capital from ordinary shares</t>
+          <t>Non-distributable</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Capital from redeemable preference shares</t>
+          <t>Capital reserve</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Capital from non-redeemable preference shares</t>
+          <t>Foreign currency translation reserve</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
-        <is>
-          <t>*Total issued capital</t>
-        </is>
-      </c>
-      <c r="B148">
-        <f>1*B145+1*B146+1*B147</f>
-        <v/>
-      </c>
-      <c r="C148">
-        <f>1*C145+1*C146+1*C147</f>
-        <v/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Revaluation surplus</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Reserves [abstract]</t>
+          <t>Other non-distributable reserves</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Non-distributable [abstract]</t>
-        </is>
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-distributable reserves</t>
+        </is>
+      </c>
+      <c r="B150">
+        <f>1*B146+1*B147+1*B148+1*B149</f>
+        <v/>
+      </c>
+      <c r="C150">
+        <f>1*C146+1*C147+1*C148+1*C149</f>
+        <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Capital reserve</t>
+          <t>Distributable</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve</t>
+          <t>Other distributable reserves</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Revaluation surplus</t>
-        </is>
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>*Total distributable reserves</t>
+        </is>
+      </c>
+      <c r="B153">
+        <f>1*B152</f>
+        <v/>
+      </c>
+      <c r="C153">
+        <f>1*C152</f>
+        <v/>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Other non-distributable reserves</t>
-        </is>
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>*Total reserves</t>
+        </is>
+      </c>
+      <c r="B154">
+        <f>1*B150+1*B153</f>
+        <v/>
+      </c>
+      <c r="C154">
+        <f>1*C150+1*C153</f>
+        <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-distributable reserves</t>
-        </is>
-      </c>
-      <c r="B155">
-        <f>1*B151+1*B152+1*B153+1*B154</f>
-        <v/>
-      </c>
-      <c r="C155">
-        <f>1*C151+1*C152+1*C153+1*C154</f>
-        <v/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Equity - others components</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Distributable [abstract]</t>
+          <t>Perpetual Sukuk</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Other distributable reserves</t>
+          <t>Equity component of Irredeemable Convertible Unsecured Loan Stocks (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="inlineStr">
-        <is>
-          <t>*Total distributable reserves</t>
-        </is>
-      </c>
-      <c r="B158">
-        <f>1*B157</f>
-        <v/>
-      </c>
-      <c r="C158">
-        <f>1*C157</f>
-        <v/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Equity component of preference shares</t>
+        </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
-        <is>
-          <t>*Total reserves</t>
-        </is>
-      </c>
-      <c r="B159">
-        <f>1*B155+1*B158</f>
-        <v/>
-      </c>
-      <c r="C159">
-        <f>1*C155+1*C158</f>
-        <v/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Equity components of other financial instruments</t>
+        </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Equity - others components [abstract]</t>
-        </is>
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>*Total equity - other components</t>
+        </is>
+      </c>
+      <c r="B160">
+        <f>1*B156+1*B157+1*B158+1*B159</f>
+        <v/>
+      </c>
+      <c r="C160">
+        <f>1*C156+1*C157+1*C158+1*C159</f>
+        <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Perpetual Sukuk</t>
+          <t>Non-current loans and borrowings</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Equity component of Irredeemable Convertible Unsecured Loan Stocks (ICULS)</t>
+          <t>Secured bank loans</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Equity component of preference shares</t>
+          <t>Unsecured bank loans</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Equity components of other financial instruments</t>
+          <t>Secured convertible notes</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
-        <is>
-          <t>*Total equity - other components</t>
-        </is>
-      </c>
-      <c r="B165">
-        <f>1*B161+1*B162+1*B163+1*B164</f>
-        <v/>
-      </c>
-      <c r="C165">
-        <f>1*C161+1*C162+1*C163+1*C164</f>
-        <v/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Unsecured convertible notes</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Non-current loans and borrowings [abstract]</t>
+          <t>Redeemable preference shares</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Secured bank loans</t>
+          <t>Finance lease liabilities</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Unsecured bank loans</t>
+          <t>Loan from holding company</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Secured convertible notes</t>
+          <t>Loan from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Unsecured convertible notes</t>
+          <t>Loan from associates</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Redeemable preference shares</t>
+          <t>Loan from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Finance lease liabilities</t>
+          <t>Loan from other related companies</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Loan from holding company</t>
+          <t>Other secured bank facilities</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Loan from subsidiaries</t>
+          <t>Other unsecured bank facilities</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Loan from associates</t>
+          <t>Other non-current borrowings</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Loan from joint ventures</t>
-        </is>
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current borrowings</t>
+        </is>
+      </c>
+      <c r="B176">
+        <f>1*B162+1*B163+1*B164+1*B165+1*B166+1*B167+1*B168+1*B169+1*B170+1*B171+1*B172+1*B173+1*B174+1*B175</f>
+        <v/>
+      </c>
+      <c r="C176">
+        <f>1*C162+1*C163+1*C164+1*C165+1*C166+1*C167+1*C168+1*C169+1*C170+1*C171+1*C172+1*C173+1*C174+1*C175</f>
+        <v/>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Loan from other related companies</t>
+          <t>Non-current employee benefits</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Other secured bank facilities</t>
+          <t>Cash-settled share-based payment liability</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Other unsecured bank facilities</t>
+          <t>Employment termination benefits</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Other non-current borrowings</t>
+          <t>Provision for unconsumed leave</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current borrowings</t>
-        </is>
-      </c>
-      <c r="B181">
-        <f>1*B167+1*B168+1*B169+1*B170+1*B171+1*B172+1*B173+1*B174+1*B175+1*B176+1*B177+1*B178+1*B179+1*B180</f>
-        <v/>
-      </c>
-      <c r="C181">
-        <f>1*C167+1*C168+1*C169+1*C170+1*C171+1*C172+1*C173+1*C174+1*C175+1*C176+1*C177+1*C178+1*C179+1*C180</f>
-        <v/>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Defined contribution plan</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Non-current employee benefits [abstract]</t>
+          <t>Defined benefit plan</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Cash-settled share-based payment liability</t>
+          <t>Other non-current employee benefits</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Employment termination benefits</t>
-        </is>
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current employee benefits</t>
+        </is>
+      </c>
+      <c r="B184">
+        <f>1*B178+1*B179+1*B180+1*B181+1*B182+1*B183</f>
+        <v/>
+      </c>
+      <c r="C184">
+        <f>1*C178+1*C179+1*C180+1*C181+1*C182+1*C183</f>
+        <v/>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Provision for unconsumed leave</t>
+          <t>Non-current provisions</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Defined contribution plan</t>
+          <t>Warranty provision</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Defined benefit plan</t>
+          <t>Restructuring provision</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Other non-current employee benefits</t>
+          <t>Legal proceedings provision</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current employee benefits</t>
-        </is>
-      </c>
-      <c r="B189">
-        <f>1*B183+1*B184+1*B185+1*B186+1*B187+1*B188</f>
-        <v/>
-      </c>
-      <c r="C189">
-        <f>1*C183+1*C184+1*C185+1*C186+1*C187+1*C188</f>
-        <v/>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Onerous contracts provision</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Non-current provisions [abstract]</t>
+          <t>Provision for decommissioning, restoration and rehabilitation costs</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Warranty provision</t>
+          <t>Other non-current provisions</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Restructuring provision</t>
-        </is>
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current provisions</t>
+        </is>
+      </c>
+      <c r="B192">
+        <f>1*B186+1*B187+1*B188+1*B189+1*B190+1*B191</f>
+        <v/>
+      </c>
+      <c r="C192">
+        <f>1*C186+1*C187+1*C188+1*C189+1*C190+1*C191</f>
+        <v/>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Legal proceedings provision</t>
+          <t>Trade and other non-current payables</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Onerous contracts provision</t>
+          <t>Non-current trade payables</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Provision for decommissioning, restoration and rehabilitation costs</t>
+          <t>Trade payables due to holding company</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Other non-current provisions</t>
+          <t>Trade payables due to subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current provisions</t>
-        </is>
-      </c>
-      <c r="B197">
-        <f>1*B191+1*B192+1*B193+1*B194+1*B195+1*B196</f>
-        <v/>
-      </c>
-      <c r="C197">
-        <f>1*C191+1*C192+1*C193+1*C194+1*C195+1*C196</f>
-        <v/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Trade payables due to associates</t>
+        </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Trade and other non-current payables [abstract]</t>
+          <t>Trade payables due to joint ventures</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Non-current trade payables [abstract]</t>
+          <t>Trade payables due to other related parties</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Trade payables due to holding company</t>
+          <t>Other non-current trade payables</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Trade payables due to subsidiaries</t>
-        </is>
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current trade payables</t>
+        </is>
+      </c>
+      <c r="B201">
+        <f>1*B195+1*B196+1*B197+1*B198+1*B199+1*B200</f>
+        <v/>
+      </c>
+      <c r="C201">
+        <f>1*C195+1*C196+1*C197+1*C198+1*C199+1*C200</f>
+        <v/>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Trade payables due to associates</t>
+          <t>Other non-current payables</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Trade payables due to joint ventures</t>
+          <t>Other non-current payables due to related parties</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Trade payables due to other related parties</t>
+          <t>Other payables due to holding company</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Other non-current trade payables</t>
+          <t>Other payables due to subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current trade payables</t>
-        </is>
-      </c>
-      <c r="B206">
-        <f>1*B200+1*B201+1*B202+1*B203+1*B204+1*B205</f>
-        <v/>
-      </c>
-      <c r="C206">
-        <f>1*C200+1*C201+1*C202+1*C203+1*C204+1*C205</f>
-        <v/>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Other payables due to associates</t>
+        </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Other non-current payables [abstract]</t>
+          <t>Other payables due to joint ventures</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Other non-current payables due to related parties [abstract]</t>
+          <t>Other payables due to other related parties</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Other payables due to holding company</t>
-        </is>
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>*Total other non-current payables due to related parties</t>
+        </is>
+      </c>
+      <c r="B209">
+        <f>1*B204+1*B205+1*B206+1*B207+1*B208</f>
+        <v/>
+      </c>
+      <c r="C209">
+        <f>1*C204+1*C205+1*C206+1*C207+1*C208</f>
+        <v/>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Other payables due to subsidiaries</t>
+          <t>Non-current non-trade payables</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Other payables due to associates</t>
+          <t>Deferred income</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Other payables due to joint ventures</t>
+          <t>Accruals</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Other payables due to other related parties</t>
+          <t>Retention payable</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="inlineStr">
-        <is>
-          <t>*Total other non-current payables due to related parties</t>
-        </is>
-      </c>
-      <c r="B214">
-        <f>1*B209+1*B210+1*B211+1*B212+1*B213</f>
-        <v/>
-      </c>
-      <c r="C214">
-        <f>1*C209+1*C210+1*C211+1*C212+1*C213</f>
-        <v/>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Other non-current non-trade payables</t>
+        </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Non-current non-trade payables [abstract]</t>
-        </is>
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-current non-trade payables</t>
+        </is>
+      </c>
+      <c r="B215">
+        <f>1*B211+1*B212+1*B213+1*B214</f>
+        <v/>
+      </c>
+      <c r="C215">
+        <f>1*C211+1*C212+1*C213+1*C214</f>
+        <v/>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Deferred income</t>
-        </is>
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>*Total other non-current payables</t>
+        </is>
+      </c>
+      <c r="B216">
+        <f>1*B209+1*B215</f>
+        <v/>
+      </c>
+      <c r="C216">
+        <f>1*C209+1*C215</f>
+        <v/>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Accruals</t>
-        </is>
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>*Total trade and other non-current payables</t>
+        </is>
+      </c>
+      <c r="B217">
+        <f>1*B201+1*B216</f>
+        <v/>
+      </c>
+      <c r="C217">
+        <f>1*C201+1*C216</f>
+        <v/>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Retention payable</t>
+          <t>Current loans and borrowings</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Other non-current non-trade payables</t>
+          <t>Secured bank loans</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-current non-trade payables</t>
-        </is>
-      </c>
-      <c r="B220">
-        <f>1*B216+1*B217+1*B218+1*B219</f>
-        <v/>
-      </c>
-      <c r="C220">
-        <f>1*C216+1*C217+1*C218+1*C219</f>
-        <v/>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Unsecured bank loans</t>
+        </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="inlineStr">
-        <is>
-          <t>*Total other non-current payables</t>
-        </is>
-      </c>
-      <c r="B221">
-        <f>1*B214+1*B220</f>
-        <v/>
-      </c>
-      <c r="C221">
-        <f>1*C214+1*C220</f>
-        <v/>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Secured convertible notes</t>
+        </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="inlineStr">
-        <is>
-          <t>*Total trade and other non-current payables</t>
-        </is>
-      </c>
-      <c r="B222">
-        <f>1*B206+1*B221</f>
-        <v/>
-      </c>
-      <c r="C222">
-        <f>1*C206+1*C221</f>
-        <v/>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Unsecured convertible notes</t>
+        </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Current loans and borrowings [abstract]</t>
+          <t>Secured bank overdrafts</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Secured bank loans</t>
+          <t>Unsecured bank overdrafts</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Unsecured bank loans</t>
+          <t>Redeemable preference shares</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Secured convertible notes</t>
+          <t>Finance lease liabilities</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Unsecured convertible notes</t>
+          <t>Loan from holding company</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Secured bank overdrafts</t>
+          <t>Loan from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Unsecured bank overdrafts</t>
+          <t>Loan from associates</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Redeemable preference shares</t>
+          <t>Loan from joint venture</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Finance lease liabilities</t>
+          <t>Loan from other related companies</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Loan from holding company</t>
+          <t>Other secured bank facilities</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Loan from subsidiaries</t>
+          <t>Other unsecured bank facilities</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Loan from associates</t>
+          <t>Other current borrowings</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Loan from joint venture</t>
-        </is>
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>*Total current loans and borrowings</t>
+        </is>
+      </c>
+      <c r="B235">
+        <f>1*B219+1*B220+1*B221+1*B222+1*B223+1*B224+1*B225+1*B226+1*B227+1*B228+1*B229+1*B230+1*B231+1*B232+1*B233+1*B234</f>
+        <v/>
+      </c>
+      <c r="C235">
+        <f>1*C219+1*C220+1*C221+1*C222+1*C223+1*C224+1*C225+1*C226+1*C227+1*C228+1*C229+1*C230+1*C231+1*C232+1*C233+1*C234</f>
+        <v/>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Loan from other related companies</t>
+          <t>Current employee benefits</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Other secured bank facilities</t>
+          <t>Cash-settled share-based payment liability</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Other unsecured bank facilities</t>
+          <t>Employment termination benefits</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Other current borrowings</t>
+          <t>Provision for unconsumed leave</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="inlineStr">
-        <is>
-          <t>*Total current loans and borrowings</t>
-        </is>
-      </c>
-      <c r="B240">
-        <f>1*B224+1*B225+1*B226+1*B227+1*B228+1*B229+1*B230+1*B231+1*B232+1*B233+1*B234+1*B235+1*B236+1*B237+1*B238+1*B239</f>
-        <v/>
-      </c>
-      <c r="C240">
-        <f>1*C224+1*C225+1*C226+1*C227+1*C228+1*C229+1*C230+1*C231+1*C232+1*C233+1*C234+1*C235+1*C236+1*C237+1*C238+1*C239</f>
-        <v/>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Defined contribution plan</t>
+        </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Current employee benefits [abstract]</t>
+          <t>Defined benefit plan</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Cash-settled share-based payment liability</t>
+          <t>Other current employee  benefits</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Employment termination benefits</t>
-        </is>
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>*Total current employee benefits</t>
+        </is>
+      </c>
+      <c r="B243">
+        <f>1*B237+1*B238+1*B239+1*B240+1*B241+1*B242</f>
+        <v/>
+      </c>
+      <c r="C243">
+        <f>1*C237+1*C238+1*C239+1*C240+1*C241+1*C242</f>
+        <v/>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Provision for unconsumed leave</t>
+          <t>Current provisions</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Defined contribution plan</t>
+          <t>Warranty provision</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Defined benefit plan</t>
+          <t>Restructuring provision</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Other current employee  benefits</t>
+          <t>Legal proceedings provision</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="inlineStr">
-        <is>
-          <t>*Total current employee benefits</t>
-        </is>
-      </c>
-      <c r="B248">
-        <f>1*B242+1*B243+1*B244+1*B245+1*B246+1*B247</f>
-        <v/>
-      </c>
-      <c r="C248">
-        <f>1*C242+1*C243+1*C244+1*C245+1*C246+1*C247</f>
-        <v/>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Onerous contracts provision</t>
+        </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Current provisions [abstract]</t>
+          <t>Provision for decommissioning, restoration and rehabilitation costs</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Warranty provision</t>
+          <t>Other current provisions</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Restructuring provision</t>
-        </is>
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>*Total current provisions</t>
+        </is>
+      </c>
+      <c r="B251">
+        <f>1*B245+1*B246+1*B247+1*B248+1*B249+1*B250</f>
+        <v/>
+      </c>
+      <c r="C251">
+        <f>1*C245+1*C246+1*C247+1*C248+1*C249+1*C250</f>
+        <v/>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Legal proceedings provision</t>
+          <t>Trade and other current payables</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Onerous contracts provision</t>
+          <t>Current trade payables</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Provision for decommissioning, restoration and rehabilitation costs</t>
+          <t>Trade payable due to contract suppliers</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Other current provisions</t>
+          <t>Trade payables due to holding company</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="inlineStr">
-        <is>
-          <t>*Total current provisions</t>
-        </is>
-      </c>
-      <c r="B256">
-        <f>1*B250+1*B251+1*B252+1*B253+1*B254+1*B255</f>
-        <v/>
-      </c>
-      <c r="C256">
-        <f>1*C250+1*C251+1*C252+1*C253+1*C254+1*C255</f>
-        <v/>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Trade payables due to subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Trade and other current payables [abstract]</t>
+          <t>Trade payables due to associates</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Current trade payables [abstract]</t>
+          <t>Trade payables due to joint ventures</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Trade payable due to contract suppliers</t>
+          <t>Trade payables due to other related parties</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Trade payables due to holding company</t>
+          <t>Other current trade payables</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Trade payables due to subsidiaries</t>
-        </is>
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>*Total current trade payables</t>
+        </is>
+      </c>
+      <c r="B261">
+        <f>1*B254+1*B255+1*B256+1*B257+1*B258+1*B259+1*B260</f>
+        <v/>
+      </c>
+      <c r="C261">
+        <f>1*C254+1*C255+1*C256+1*C257+1*C258+1*C259+1*C260</f>
+        <v/>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Trade payables due to associates</t>
+          <t>Other current payables</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Trade payables due to joint ventures</t>
+          <t>Other current payables due to related parties</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Trade payables due to other related parties</t>
+          <t>Other payables due to holding company</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Other current trade payables</t>
+          <t>Other payables due to subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="inlineStr">
-        <is>
-          <t>*Total current trade payables</t>
-        </is>
-      </c>
-      <c r="B266">
-        <f>1*B259+1*B260+1*B261+1*B262+1*B263+1*B264+1*B265</f>
-        <v/>
-      </c>
-      <c r="C266">
-        <f>1*C259+1*C260+1*C261+1*C262+1*C263+1*C264+1*C265</f>
-        <v/>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Other payables due to associates</t>
+        </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Other current payables [abstract]</t>
+          <t>Other payables due to joint ventures</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Other current payables due to related parties [abstract]</t>
+          <t>Other payables due to other related parties</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Other payables due to holding company</t>
-        </is>
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>*Total other current payables due to related parties</t>
+        </is>
+      </c>
+      <c r="B269">
+        <f>1*B264+1*B265+1*B266+1*B267+1*B268</f>
+        <v/>
+      </c>
+      <c r="C269">
+        <f>1*C264+1*C265+1*C266+1*C267+1*C268</f>
+        <v/>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Other payables due to subsidiaries</t>
+          <t>Current non-trade payables</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Other payables due to associates</t>
+          <t>Deferred income</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Other payables due to joint ventures</t>
+          <t>Accruals</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Other payables due to other related parties</t>
+          <t>Retention payable</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="inlineStr">
-        <is>
-          <t>*Total other current payables due to related parties</t>
-        </is>
-      </c>
-      <c r="B274">
-        <f>1*B269+1*B270+1*B271+1*B272+1*B273</f>
-        <v/>
-      </c>
-      <c r="C274">
-        <f>1*C269+1*C270+1*C271+1*C272+1*C273</f>
-        <v/>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Other current non-trade payables</t>
+        </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Current non-trade payables [abstract]</t>
-        </is>
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>*Total current non-trade payables</t>
+        </is>
+      </c>
+      <c r="B275">
+        <f>1*B271+1*B272+1*B273+1*B274</f>
+        <v/>
+      </c>
+      <c r="C275">
+        <f>1*C271+1*C272+1*C273+1*C274</f>
+        <v/>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Deferred income</t>
-        </is>
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>*Total other current payables</t>
+        </is>
+      </c>
+      <c r="B276">
+        <f>1*B269+1*B275</f>
+        <v/>
+      </c>
+      <c r="C276">
+        <f>1*C269+1*C275</f>
+        <v/>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Accruals</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Retention payable</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Other current non-trade payables</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="1" t="inlineStr">
-        <is>
-          <t>*Total current non-trade payables</t>
-        </is>
-      </c>
-      <c r="B280">
-        <f>1*B276+1*B277+1*B278+1*B279</f>
-        <v/>
-      </c>
-      <c r="C280">
-        <f>1*C276+1*C277+1*C278+1*C279</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="1" t="inlineStr">
-        <is>
-          <t>*Total other current payables</t>
-        </is>
-      </c>
-      <c r="B281">
-        <f>1*B274+1*B280</f>
-        <v/>
-      </c>
-      <c r="C281">
-        <f>1*C274+1*C280</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="1" t="inlineStr">
+      <c r="A277" s="1" t="inlineStr">
         <is>
           <t>*Total trade and other current payables</t>
         </is>
       </c>
-      <c r="B282">
-        <f>1*B266+1*B281</f>
-        <v/>
-      </c>
-      <c r="C282">
-        <f>1*C266+1*C281</f>
+      <c r="B277">
+        <f>1*B261+1*B276</f>
+        <v/>
+      </c>
+      <c r="C277">
+        <f>1*C261+1*C276</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Company/01-SOFP-CuNonCu.xlsx
+++ b/XBRL-template-MPERS/Company/01-SOFP-CuNonCu.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +28,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,28 +456,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Non-current assets</t>
         </is>
@@ -606,7 +617,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>*Total non-current assets</t>
         </is>
@@ -621,7 +632,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Current assets</t>
         </is>
@@ -708,7 +719,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>*Total current assets</t>
         </is>
@@ -723,7 +734,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>*Total assets</t>
         </is>
@@ -738,14 +749,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Equity and liabilities</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
@@ -796,7 +807,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>*Total equity attributable to owners</t>
         </is>
@@ -833,7 +844,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>*Total equity</t>
         </is>
@@ -848,14 +859,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>Non-current liabilities</t>
         </is>
@@ -936,7 +947,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>*Total non-current liabilities</t>
         </is>
@@ -951,7 +962,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>Current liabilities</t>
         </is>
@@ -1039,7 +1050,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>*Total current liabilities</t>
         </is>
@@ -1054,7 +1065,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>*Total liabilities</t>
         </is>
@@ -1069,7 +1080,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>*Total equity and liabilities</t>
         </is>
@@ -1121,42 +1132,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Land and buildings</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
@@ -1184,7 +1195,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>*Total land</t>
         </is>
@@ -1199,7 +1210,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Buildings</t>
         </is>
@@ -1234,7 +1245,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>*Total buildings</t>
         </is>
@@ -1249,7 +1260,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>*Total land and buildings</t>
         </is>
@@ -1306,7 +1317,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>*Total property, plant and equipment</t>
         </is>
@@ -1321,7 +1332,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Investment properties</t>
         </is>
@@ -1363,7 +1374,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>*Total investment properties</t>
         </is>
@@ -1378,14 +1389,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Intangible assets and goodwill</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Intangible assets other than goodwill</t>
         </is>
@@ -1406,7 +1417,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>*Total intangible assets other than goodwill</t>
         </is>
@@ -1428,7 +1439,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>*Total intangible assets and goodwill</t>
         </is>
@@ -1443,7 +1454,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>Investments in subsidiaries</t>
         </is>
@@ -1478,7 +1489,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>*Total investments in subsidiaries</t>
         </is>
@@ -1493,7 +1504,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Investments in associates</t>
         </is>
@@ -1535,7 +1546,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>*Total investments in associates</t>
         </is>
@@ -1550,7 +1561,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>Investments in joint ventures</t>
         </is>
@@ -1592,7 +1603,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>*Total of investments in joint ventures</t>
         </is>
@@ -1607,14 +1618,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>Trade and other non-current receivables</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Non-current trade receivables</t>
         </is>
@@ -1663,7 +1674,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>*Total non-current trade receivables</t>
         </is>
@@ -1678,14 +1689,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="1" t="inlineStr">
         <is>
           <t>Other non-current receivables</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="1" t="inlineStr">
         <is>
           <t>Other non-current receivables due from related parties</t>
         </is>
@@ -1727,7 +1738,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>*Total other non-current receivables due from related parties</t>
         </is>
@@ -1742,7 +1753,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
         <is>
           <t>Non-current non-trade receivables</t>
         </is>
@@ -1770,7 +1781,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>*Total other non-current non-trade receivables</t>
         </is>
@@ -1785,7 +1796,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>*Total other non-current receivables</t>
         </is>
@@ -1800,7 +1811,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>*Total trade and other non-current receivables</t>
         </is>
@@ -1815,7 +1826,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="1" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
@@ -1857,7 +1868,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>*Total inventories</t>
         </is>
@@ -1872,14 +1883,14 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="inlineStr">
         <is>
           <t>Trade and other current receivables</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="inlineStr">
         <is>
           <t>Current trade receivables</t>
         </is>
@@ -1935,7 +1946,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>*Total current trade receivables</t>
         </is>
@@ -1950,14 +1961,14 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>Other current receivables</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>Current other receivables due from related parties</t>
         </is>
@@ -1999,7 +2010,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>*Total current other receivables due from related parties</t>
         </is>
@@ -2014,7 +2025,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="1" t="inlineStr">
         <is>
           <t>Current prepayments and current accrued income</t>
         </is>
@@ -2035,7 +2046,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>*Total current prepayments and current accrued income</t>
         </is>
@@ -2050,7 +2061,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="1" t="inlineStr">
         <is>
           <t>Current non-trade receivables</t>
         </is>
@@ -2092,7 +2103,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>*Total non trade receivables</t>
         </is>
@@ -2107,7 +2118,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>*Total other current receivables</t>
         </is>
@@ -2122,7 +2133,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>*Total trade and other current receivables</t>
         </is>
@@ -2137,14 +2148,14 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="1" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="1" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
@@ -2165,7 +2176,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>*Total cash</t>
         </is>
@@ -2180,7 +2191,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="1" t="inlineStr">
         <is>
           <t>Cash equivalents</t>
         </is>
@@ -2236,7 +2247,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>*Total cash equivalents</t>
         </is>
@@ -2258,7 +2269,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>*Total cash and cash equivalents</t>
         </is>
@@ -2273,7 +2284,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="1" t="inlineStr">
         <is>
           <t>Issued capital</t>
         </is>
@@ -2301,7 +2312,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>*Total issued capital</t>
         </is>
@@ -2316,14 +2327,14 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="1" t="inlineStr">
         <is>
           <t>Reserves</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="1" t="inlineStr">
         <is>
           <t>Non-distributable</t>
         </is>
@@ -2358,7 +2369,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>*Total non-distributable reserves</t>
         </is>
@@ -2373,7 +2384,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="1" t="inlineStr">
         <is>
           <t>Distributable</t>
         </is>
@@ -2387,7 +2398,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>*Total distributable reserves</t>
         </is>
@@ -2402,7 +2413,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>*Total reserves</t>
         </is>
@@ -2417,7 +2428,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="1" t="inlineStr">
         <is>
           <t>Equity - others components</t>
         </is>
@@ -2452,7 +2463,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>*Total equity - other components</t>
         </is>
@@ -2467,7 +2478,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="1" t="inlineStr">
         <is>
           <t>Non-current loans and borrowings</t>
         </is>
@@ -2572,7 +2583,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>*Total non-current borrowings</t>
         </is>
@@ -2587,7 +2598,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="1" t="inlineStr">
         <is>
           <t>Non-current employee benefits</t>
         </is>
@@ -2636,7 +2647,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>*Total non-current employee benefits</t>
         </is>
@@ -2651,7 +2662,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="1" t="inlineStr">
         <is>
           <t>Non-current provisions</t>
         </is>
@@ -2700,7 +2711,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>*Total non-current provisions</t>
         </is>
@@ -2715,14 +2726,14 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="1" t="inlineStr">
         <is>
           <t>Trade and other non-current payables</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="1" t="inlineStr">
         <is>
           <t>Non-current trade payables</t>
         </is>
@@ -2771,7 +2782,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>*Total non-current trade payables</t>
         </is>
@@ -2786,14 +2797,14 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="1" t="inlineStr">
         <is>
           <t>Other non-current payables</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="1" t="inlineStr">
         <is>
           <t>Other non-current payables due to related parties</t>
         </is>
@@ -2835,7 +2846,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>*Total other non-current payables due to related parties</t>
         </is>
@@ -2850,7 +2861,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="1" t="inlineStr">
         <is>
           <t>Non-current non-trade payables</t>
         </is>
@@ -2885,7 +2896,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>*Total non-current non-trade payables</t>
         </is>
@@ -2900,7 +2911,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>*Total other non-current payables</t>
         </is>
@@ -2915,7 +2926,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>*Total trade and other non-current payables</t>
         </is>
@@ -2930,7 +2941,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="1" t="inlineStr">
         <is>
           <t>Current loans and borrowings</t>
         </is>
@@ -3049,7 +3060,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>*Total current loans and borrowings</t>
         </is>
@@ -3064,7 +3075,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="1" t="inlineStr">
         <is>
           <t>Current employee benefits</t>
         </is>
@@ -3113,7 +3124,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="inlineStr">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>*Total current employee benefits</t>
         </is>
@@ -3128,7 +3139,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="1" t="inlineStr">
         <is>
           <t>Current provisions</t>
         </is>
@@ -3177,7 +3188,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>*Total current provisions</t>
         </is>
@@ -3192,14 +3203,14 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="1" t="inlineStr">
         <is>
           <t>Trade and other current payables</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="1" t="inlineStr">
         <is>
           <t>Current trade payables</t>
         </is>
@@ -3255,7 +3266,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>*Total current trade payables</t>
         </is>
@@ -3270,14 +3281,14 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="1" t="inlineStr">
         <is>
           <t>Other current payables</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="1" t="inlineStr">
         <is>
           <t>Other current payables due to related parties</t>
         </is>
@@ -3319,7 +3330,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="inlineStr">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>*Total other current payables due to related parties</t>
         </is>
@@ -3334,7 +3345,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="1" t="inlineStr">
         <is>
           <t>Current non-trade payables</t>
         </is>
@@ -3369,7 +3380,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>*Total current non-trade payables</t>
         </is>
@@ -3384,7 +3395,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>*Total other current payables</t>
         </is>
@@ -3399,7 +3410,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>*Total trade and other current payables</t>
         </is>
